--- a/tests/fixtures/standard.xlsx
+++ b/tests/fixtures/standard.xlsx
@@ -442,7 +442,7 @@
         <v>김서연</v>
       </c>
       <c r="G2" t="str">
-        <v>학생은 모둠 토의에서 자료를 정리했고, 유튜브 영상을 참고함. ‘토지’를 읽고 반론(counterargument)을 제시함.</v>
+        <v>학생은 모둠 토의에서 자료를 정리했고, 구글 문서로 발표문을 작성함. 유튜브 영상을 참고하여 ‘토지’를 읽고 반론(counterargument)을 제시함.</v>
       </c>
     </row>
     <row r="3">
